--- a/dataset/01.w_Defects/memory_leak.xlsx
+++ b/dataset/01.w_Defects/memory_leak.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>typedef struct { int a; int b; } memory_leak_0013_s_001; typedef union { memory_leak_0013_s_001 *s1; memory_leak_0013_s_002 *s2; memory_leak_0013_s_003 *s3; } memory_leak_0013_uni_001; void *vptr; static unsigned char a =INDEX; char * memory_leak_0016_gbl_ptr; long ** memory_leak_0017_gbl_doubleptr; char **memory_leak_0018dst; extern volatile int vflag; void memory_leak_0013 () { memory_leak_0013_uni_001 *u = (memory_leak_0013_uni_001 * )malloc(5*sizeof( memory_leak_0013_uni_001 )); if(u!=NULL) { u-&gt;s1 = (memory_leak_0013_s_001 *) malloc(sizeof(memory_leak_0013_s_001)); } memory_leak_0013_uni_001 *p = (memory_leak_0013_uni_001 * )malloc(5*sizeof( memory_leak_0013_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory Leakage */ p-&gt;s1 = (memory_leak_0013_s_001 *) malloc(sizeof(memory_leak_0013_s_001)); if(u!=NULL) { p = u; p-&gt;s1-&gt;a = 1; free(p-&gt;s1); free(p); } }</t>
+          <t>typedef union { memory_leak_0013_s_001 *s1; memory_leak_0013_s_002 *s2; memory_leak_0013_s_003 *s3; } memory_leak_0013_uni_001; typedef struct { int a; int b; } memory_leak_0013_s_001; void *vptr; static unsigned char a =INDEX; char * memory_leak_0016_gbl_ptr; long ** memory_leak_0017_gbl_doubleptr; char **memory_leak_0018dst; extern volatile int vflag; void memory_leak_0013 () { memory_leak_0013_uni_001 *u = (memory_leak_0013_uni_001 * )malloc(5*sizeof( memory_leak_0013_uni_001 )); if(u!=NULL) { u-&gt;s1 = (memory_leak_0013_s_001 *) malloc(sizeof(memory_leak_0013_s_001)); } memory_leak_0013_uni_001 *p = (memory_leak_0013_uni_001 * )malloc(5*sizeof( memory_leak_0013_uni_001 )); /*Tool should detect this line as error*/ /*ERROR:Memory Leakage */ p-&gt;s1 = (memory_leak_0013_s_001 *) malloc(sizeof(memory_leak_0013_s_001)); if(u!=NULL) { p = u; p-&gt;s1-&gt;a = 1; free(p-&gt;s1); free(p); } }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
